--- a/data/gravel/Sanitas Node Gravel SG Ti 2025.xlsx
+++ b/data/gravel/Sanitas Node Gravel SG Ti 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FDBA49E-FB59-1C44-BBFC-BCC939B29C13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BC3A89C-BA9A-0C43-89B1-1443E0E92D69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="35020" yWindow="-23880" windowWidth="25900" windowHeight="14700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="112">
   <si>
     <t>brand</t>
   </si>
@@ -275,9 +275,6 @@
     <t>Node Gravel SG Ti</t>
   </si>
   <si>
-    <t>https://sanitasbikes.com/product/node-sg-gravel-titanium/</t>
-  </si>
-  <si>
     <t>Size</t>
   </si>
   <si>
@@ -366,6 +363,12 @@
   </si>
   <si>
     <t>a8:h33</t>
+  </si>
+  <si>
+    <t>https://www.sanitasbikes.com/multi-surface-gravel</t>
+  </si>
+  <si>
+    <t>https://images.squarespace-cdn.com/content/v1/683892ca9490732d748fc31b/76e82567-8571-416d-b6a6-da1f4b94769a/DSCF4197.JPG?format=2500w</t>
   </si>
 </sst>
 </file>
@@ -819,7 +822,12 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>80</v>
+        <v>110</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B6" s="2" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.3">
@@ -827,7 +835,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8" spans="1:22" ht="22" x14ac:dyDescent="0.3">
@@ -835,25 +843,25 @@
         <v>6</v>
       </c>
       <c r="B8" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="C8" s="11" t="s">
         <v>81</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>82</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>77</v>
       </c>
       <c r="E8" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="F8" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="G8" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="G8" s="11" t="s">
+      <c r="H8" s="11" t="s">
         <v>85</v>
-      </c>
-      <c r="H8" s="11" t="s">
-        <v>86</v>
       </c>
       <c r="I8" s="7"/>
       <c r="J8" s="7"/>
@@ -875,7 +883,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C9" s="12">
         <v>518</v>
@@ -913,7 +921,7 @@
         <v>11</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C10" s="12">
         <v>70.5</v>
@@ -951,7 +959,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C11" s="12">
         <v>74</v>
@@ -986,10 +994,10 @@
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C12" s="12">
         <f>VALUE(LEFT(I12,3))</f>
@@ -1016,22 +1024,22 @@
         <v>540</v>
       </c>
       <c r="I12" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="J12" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="J12" s="10" t="s">
+      <c r="K12" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="K12" s="10" t="s">
+      <c r="L12" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="L12" s="10" t="s">
+      <c r="M12" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="M12" s="10" t="s">
+      <c r="N12" s="10" t="s">
         <v>94</v>
-      </c>
-      <c r="N12" s="10" t="s">
-        <v>95</v>
       </c>
       <c r="O12" s="5"/>
       <c r="P12" s="5"/>
@@ -1045,7 +1053,7 @@
         <v>9</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C13" s="12">
         <f>VALUE(RIGHT(I12,3))</f>
@@ -1089,7 +1097,7 @@
         <v>10</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C14" s="12">
         <v>95</v>
@@ -1127,7 +1135,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C15" s="12">
         <v>425</v>
@@ -1165,7 +1173,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C16" s="12">
         <v>75</v>
@@ -1203,7 +1211,7 @@
         <v>18</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C17" s="12">
         <v>754</v>
@@ -1241,7 +1249,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C18" s="12">
         <v>363.6</v>
@@ -1280,7 +1288,7 @@
         <v>16</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C19" s="12">
         <v>531.79999999999995</v>
@@ -1360,7 +1368,7 @@
         <v>395</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J21" s="8"/>
       <c r="K21" s="8"/>
@@ -1659,7 +1667,7 @@
         <v>33</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
@@ -1729,7 +1737,7 @@
         <v>44</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
@@ -1786,7 +1794,7 @@
         <v>53</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
@@ -1868,7 +1876,7 @@
         <v>67</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Sanitas Node Gravel SG Ti 2025.xlsx
+++ b/data/gravel/Sanitas Node Gravel SG Ti 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BC3A89C-BA9A-0C43-89B1-1443E0E92D69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45B361F8-FF46-9544-8860-B1D805B4BF55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="35020" yWindow="-23880" windowWidth="25900" windowHeight="14700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="114">
   <si>
     <t>brand</t>
   </si>
@@ -369,13 +369,19 @@
   </si>
   <si>
     <t>https://images.squarespace-cdn.com/content/v1/683892ca9490732d748fc31b/76e82567-8571-416d-b6a6-da1f4b94769a/DSCF4197.JPG?format=2500w</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Durango, Colorado, USA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <color rgb="FF000000"/>
@@ -444,6 +450,12 @@
       <color rgb="FF191919"/>
       <name val="Futura Medium"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Futura"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -465,7 +477,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -480,6 +492,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -776,7 +789,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V73"/>
+  <dimension ref="A1:V74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="2" customWidth="1"/>
@@ -1879,6 +1892,14 @@
         <v>108</v>
       </c>
     </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="B74" s="14" t="s">
+        <v>113</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Sanitas Node Gravel SG Ti 2025.xlsx
+++ b/data/gravel/Sanitas Node Gravel SG Ti 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45B361F8-FF46-9544-8860-B1D805B4BF55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DD2E4E8-0F71-2C4F-A55E-01B405382D17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="120">
   <si>
     <t>brand</t>
   </si>
@@ -375,6 +375,24 @@
   </si>
   <si>
     <t>Durango, Colorado, USA</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -789,7 +807,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V74"/>
+  <dimension ref="A1:V80"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="2" customWidth="1"/>
@@ -1747,156 +1765,186 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>45</v>
+        <v>115</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B52" s="2">
-        <v>31.6</v>
+        <v>116</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>74</v>
+        <v>117</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>48</v>
+        <v>118</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>49</v>
+        <v>119</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>50</v>
+        <v>44</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B57" s="2">
-        <v>160</v>
+        <v>45</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>52</v>
+        <v>46</v>
+      </c>
+      <c r="B58" s="2">
+        <v>31.6</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>105</v>
+        <v>74</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B63" s="2">
-        <v>2</v>
+        <v>160</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
+      </c>
+      <c r="B69" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B70" s="2">
-        <v>2995</v>
+        <v>58</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B71" s="2">
-        <v>5950</v>
+        <v>59</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B76" s="2">
+        <v>2995</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B77" s="2">
+        <v>5950</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B73" s="2" t="s">
+      <c r="B79" s="2" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A74" s="14" t="s">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="B74" s="14" t="s">
+      <c r="B80" s="14" t="s">
         <v>113</v>
       </c>
     </row>
